--- a/data-vh/Неделя_20.07-26.07_2026_ВХ.xlsx
+++ b/data-vh/Неделя_20.07-26.07_2026_ВХ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Отделы\Дирекция по организационному развитию и системе менеджмента качества\ОРСМК\Несоответствия\Инструкции и классификаторы\МОЕ\ИИ\Аналитика данных по качеству\Месяц ВХ\Для сайта\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4FC4DE-8626-42B3-A781-90E777EBF1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F88A0A-1775-4D8E-8AC7-3B2C9AFF2F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -322,9 +322,6 @@
     <t>Дефекты сварных швов:    - брызги металла;     - поры.    Доработаны в процессе контроля.</t>
   </si>
   <si>
-    <t>Поставщик/ переработчик</t>
-  </si>
-  <si>
     <t>Переработчик</t>
   </si>
   <si>
@@ -344,18 +341,16 @@
   </si>
   <si>
     <t>2 221,5</t>
+  </si>
+  <si>
+    <t>Поставщик/переработчик</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -372,6 +367,12 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -444,7 +445,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -461,13 +462,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -476,26 +471,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -835,11 +824,11 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -879,10 +868,10 @@
       <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -895,12 +884,12 @@
         <v>18</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="12">
         <v>1.9730000000000001</v>
       </c>
       <c r="L2" s="5" t="s">
@@ -923,10 +912,10 @@
       <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="5" t="s">
@@ -939,12 +928,10 @@
         <v>26</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="J3" s="7">
-        <v>12725</v>
-      </c>
-      <c r="K3" s="7">
+        <v>100</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="12">
         <v>12725</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -967,10 +954,10 @@
       <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="5" t="s">
@@ -983,12 +970,12 @@
         <v>34</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="3">
         <v>16</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="12">
         <v>40.96</v>
       </c>
       <c r="L4" s="5" t="s">
@@ -1011,10 +998,10 @@
       <c r="C5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F5" s="5" t="s">
@@ -1027,12 +1014,12 @@
         <v>37</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J5" s="3">
         <v>32</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="12">
         <v>8.64</v>
       </c>
       <c r="L5" s="5" t="s">
@@ -1055,11 +1042,11 @@
       <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>100</v>
+      <c r="E6" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>41</v>
@@ -1071,12 +1058,12 @@
         <v>43</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J6" s="3">
         <v>40</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="12">
         <v>7320</v>
       </c>
       <c r="L6" s="5" t="s">
@@ -1099,11 +1086,11 @@
       <c r="C7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>100</v>
+      <c r="E7" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>49</v>
@@ -1115,12 +1102,12 @@
         <v>43</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J7" s="3">
         <v>15</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="12">
         <v>2745</v>
       </c>
       <c r="L7" s="5" t="s">
@@ -1143,9 +1130,9 @@
       <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="12" t="s">
-        <v>100</v>
+      <c r="D8" s="7"/>
+      <c r="E8" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>54</v>
@@ -1157,12 +1144,12 @@
         <v>55</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="10">
+        <v>103</v>
+      </c>
+      <c r="J8" s="8">
         <v>1</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="11">
         <v>867.52</v>
       </c>
       <c r="L8" s="5" t="s">
@@ -1185,9 +1172,9 @@
       <c r="C9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="12" t="s">
-        <v>100</v>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>54</v>
@@ -1199,12 +1186,12 @@
         <v>57</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="10">
+        <v>103</v>
+      </c>
+      <c r="J9" s="8">
         <v>1</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="11">
         <v>512.13</v>
       </c>
       <c r="L9" s="5" t="s">
@@ -1227,9 +1214,9 @@
       <c r="C10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="12" t="s">
-        <v>100</v>
+      <c r="D10" s="7"/>
+      <c r="E10" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>60</v>
@@ -1241,12 +1228,12 @@
         <v>61</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="3">
         <v>1</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K10" s="12">
         <v>1.43</v>
       </c>
       <c r="L10" s="5" t="s">
@@ -1269,9 +1256,9 @@
       <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="12" t="s">
-        <v>100</v>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>60</v>
@@ -1283,12 +1270,12 @@
         <v>63</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="3">
         <v>1</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="12">
         <v>187.18</v>
       </c>
       <c r="L11" s="5" t="s">
@@ -1311,9 +1298,9 @@
       <c r="C12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="12" t="s">
-        <v>100</v>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>60</v>
@@ -1325,12 +1312,12 @@
         <v>64</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3">
         <v>1</v>
       </c>
-      <c r="K12" s="8">
+      <c r="K12" s="12">
         <v>31.33</v>
       </c>
       <c r="L12" s="5" t="s">
@@ -1353,9 +1340,9 @@
       <c r="C13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="12" t="s">
-        <v>100</v>
+      <c r="D13" s="7"/>
+      <c r="E13" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>60</v>
@@ -1367,12 +1354,12 @@
         <v>65</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="3">
         <v>1</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K13" s="12">
         <v>27.07</v>
       </c>
       <c r="L13" s="5" t="s">
@@ -1395,9 +1382,9 @@
       <c r="C14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="12" t="s">
-        <v>100</v>
+      <c r="D14" s="7"/>
+      <c r="E14" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>60</v>
@@ -1409,12 +1396,12 @@
         <v>66</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J14" s="3">
         <v>1</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="12">
         <v>23.52</v>
       </c>
       <c r="L14" s="5" t="s">
@@ -1437,9 +1424,9 @@
       <c r="C15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="12" t="s">
-        <v>100</v>
+      <c r="D15" s="7"/>
+      <c r="E15" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>60</v>
@@ -1451,12 +1438,12 @@
         <v>67</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" s="3">
         <v>1</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="12">
         <v>19.82</v>
       </c>
       <c r="L15" s="5" t="s">
@@ -1479,9 +1466,9 @@
       <c r="C16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="12" t="s">
-        <v>100</v>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>60</v>
@@ -1493,12 +1480,12 @@
         <v>68</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J16" s="3">
         <v>1</v>
       </c>
-      <c r="K16" s="8">
+      <c r="K16" s="12">
         <v>15.84</v>
       </c>
       <c r="L16" s="5" t="s">
@@ -1521,9 +1508,9 @@
       <c r="C17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="12" t="s">
-        <v>100</v>
+      <c r="D17" s="7"/>
+      <c r="E17" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>60</v>
@@ -1535,12 +1522,12 @@
         <v>69</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J17" s="3">
         <v>1</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K17" s="12">
         <v>95.84</v>
       </c>
       <c r="L17" s="5" t="s">
@@ -1563,9 +1550,9 @@
       <c r="C18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="12" t="s">
-        <v>100</v>
+      <c r="D18" s="7"/>
+      <c r="E18" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>60</v>
@@ -1577,12 +1564,12 @@
         <v>70</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J18" s="3">
         <v>2</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="12">
         <v>170.62</v>
       </c>
       <c r="L18" s="5" t="s">
@@ -1605,9 +1592,9 @@
       <c r="C19" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="12" t="s">
-        <v>100</v>
+      <c r="D19" s="7"/>
+      <c r="E19" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>60</v>
@@ -1619,12 +1606,12 @@
         <v>71</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J19" s="3">
         <v>2</v>
       </c>
-      <c r="K19" s="8">
+      <c r="K19" s="12">
         <v>29.56</v>
       </c>
       <c r="L19" s="5" t="s">
@@ -1647,9 +1634,9 @@
       <c r="C20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="12" t="s">
-        <v>100</v>
+      <c r="D20" s="7"/>
+      <c r="E20" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>60</v>
@@ -1661,12 +1648,12 @@
         <v>72</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J20" s="3">
         <v>2</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="12">
         <v>35.200000000000003</v>
       </c>
       <c r="L20" s="5" t="s">
@@ -1689,9 +1676,9 @@
       <c r="C21" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="12" t="s">
-        <v>100</v>
+      <c r="D21" s="7"/>
+      <c r="E21" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>60</v>
@@ -1703,12 +1690,12 @@
         <v>73</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J21" s="3">
         <v>2</v>
       </c>
-      <c r="K21" s="11">
+      <c r="K21" s="12">
         <v>41.2</v>
       </c>
       <c r="L21" s="5" t="s">
@@ -1731,9 +1718,9 @@
       <c r="C22" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="12" t="s">
-        <v>100</v>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>60</v>
@@ -1745,12 +1732,12 @@
         <v>74</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="3">
         <v>1</v>
       </c>
-      <c r="K22" s="8">
+      <c r="K22" s="12">
         <v>6.12</v>
       </c>
       <c r="L22" s="5" t="s">
@@ -1773,9 +1760,9 @@
       <c r="C23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="12" t="s">
-        <v>100</v>
+      <c r="D23" s="7"/>
+      <c r="E23" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>60</v>
@@ -1787,12 +1774,12 @@
         <v>75</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J23" s="3">
         <v>2</v>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="12">
         <v>10.62</v>
       </c>
       <c r="L23" s="5" t="s">
@@ -1815,9 +1802,9 @@
       <c r="C24" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="12" t="s">
-        <v>100</v>
+      <c r="D24" s="7"/>
+      <c r="E24" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>60</v>
@@ -1829,12 +1816,12 @@
         <v>76</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J24" s="3">
         <v>1</v>
       </c>
-      <c r="K24" s="8">
+      <c r="K24" s="12">
         <v>23.28</v>
       </c>
       <c r="L24" s="5" t="s">
@@ -1857,9 +1844,9 @@
       <c r="C25" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="12" t="s">
-        <v>100</v>
+      <c r="D25" s="7"/>
+      <c r="E25" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>60</v>
@@ -1871,12 +1858,12 @@
         <v>77</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J25" s="3">
         <v>1</v>
       </c>
-      <c r="K25" s="8">
+      <c r="K25" s="12">
         <v>1.87</v>
       </c>
       <c r="L25" s="5" t="s">
@@ -1899,9 +1886,9 @@
       <c r="C26" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="12" t="s">
-        <v>100</v>
+      <c r="D26" s="7"/>
+      <c r="E26" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>60</v>
@@ -1913,12 +1900,12 @@
         <v>78</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J26" s="3">
         <v>1</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="12">
         <v>16.690000000000001</v>
       </c>
       <c r="L26" s="5" t="s">
@@ -1941,9 +1928,9 @@
       <c r="C27" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="12" t="s">
-        <v>100</v>
+      <c r="D27" s="7"/>
+      <c r="E27" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>60</v>
@@ -1955,12 +1942,12 @@
         <v>79</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J27" s="3">
         <v>2</v>
       </c>
-      <c r="K27" s="8">
+      <c r="K27" s="12">
         <v>48.32</v>
       </c>
       <c r="L27" s="5" t="s">
@@ -1983,9 +1970,9 @@
       <c r="C28" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="12" t="s">
-        <v>100</v>
+      <c r="D28" s="7"/>
+      <c r="E28" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>60</v>
@@ -1997,12 +1984,12 @@
         <v>80</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J28" s="3">
         <v>2</v>
       </c>
-      <c r="K28" s="8">
+      <c r="K28" s="12">
         <v>48.32</v>
       </c>
       <c r="L28" s="5" t="s">
@@ -2025,9 +2012,9 @@
       <c r="C29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="12" t="s">
-        <v>100</v>
+      <c r="D29" s="7"/>
+      <c r="E29" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>60</v>
@@ -2039,12 +2026,12 @@
         <v>81</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J29" s="3">
         <v>1</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="12">
         <v>590.32000000000005</v>
       </c>
       <c r="L29" s="5" t="s">
@@ -2067,9 +2054,9 @@
       <c r="C30" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="12" t="s">
-        <v>100</v>
+      <c r="D30" s="7"/>
+      <c r="E30" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>60</v>
@@ -2081,12 +2068,12 @@
         <v>82</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J30" s="3">
         <v>2</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="12">
         <v>11.84</v>
       </c>
       <c r="L30" s="5" t="s">
@@ -2109,9 +2096,9 @@
       <c r="C31" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="12" t="s">
-        <v>100</v>
+      <c r="D31" s="7"/>
+      <c r="E31" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>60</v>
@@ -2123,12 +2110,12 @@
         <v>83</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J31" s="3">
         <v>1</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K31" s="12">
         <v>5.92</v>
       </c>
       <c r="L31" s="5" t="s">
@@ -2151,9 +2138,9 @@
       <c r="C32" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="12" t="s">
-        <v>100</v>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>60</v>
@@ -2165,12 +2152,12 @@
         <v>84</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J32" s="3">
         <v>2</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="12">
         <v>172.48</v>
       </c>
       <c r="L32" s="5" t="s">
@@ -2193,9 +2180,9 @@
       <c r="C33" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="12" t="s">
-        <v>100</v>
+      <c r="D33" s="7"/>
+      <c r="E33" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>54</v>
@@ -2207,13 +2194,13 @@
         <v>85</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J33" s="10">
+        <v>103</v>
+      </c>
+      <c r="J33" s="8">
         <v>2</v>
       </c>
-      <c r="K33" s="10" t="s">
-        <v>106</v>
+      <c r="K33" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>50</v>
@@ -2235,9 +2222,9 @@
       <c r="C34" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="12" t="s">
-        <v>100</v>
+      <c r="D34" s="7"/>
+      <c r="E34" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>54</v>
@@ -2249,12 +2236,12 @@
         <v>87</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J34" s="10">
+        <v>103</v>
+      </c>
+      <c r="J34" s="8">
         <v>1</v>
       </c>
-      <c r="K34" s="15">
+      <c r="K34" s="11">
         <v>1217.0999999999999</v>
       </c>
       <c r="L34" s="5" t="s">
@@ -2277,9 +2264,9 @@
       <c r="C35" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="12" t="s">
-        <v>100</v>
+      <c r="D35" s="7"/>
+      <c r="E35" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>54</v>
@@ -2291,12 +2278,12 @@
         <v>89</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="J35" s="10">
+        <v>102</v>
+      </c>
+      <c r="J35" s="8">
         <v>1</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="11">
         <v>1745.42</v>
       </c>
       <c r="L35" s="5" t="s">
@@ -2319,9 +2306,9 @@
       <c r="C36" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="12" t="s">
-        <v>100</v>
+      <c r="D36" s="7"/>
+      <c r="E36" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>54</v>
@@ -2333,12 +2320,12 @@
         <v>91</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="J36" s="10">
+        <v>102</v>
+      </c>
+      <c r="J36" s="8">
         <v>1</v>
       </c>
-      <c r="K36" s="17">
+      <c r="K36" s="11">
         <v>626.29999999999995</v>
       </c>
       <c r="L36" s="5" t="s">
@@ -2361,9 +2348,9 @@
       <c r="C37" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="12" t="s">
-        <v>100</v>
+      <c r="D37" s="7"/>
+      <c r="E37" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>54</v>
@@ -2375,12 +2362,12 @@
         <v>94</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="J37" s="10">
+        <v>102</v>
+      </c>
+      <c r="J37" s="8">
         <v>1</v>
       </c>
-      <c r="K37" s="17">
+      <c r="K37" s="11">
         <v>626.29999999999995</v>
       </c>
       <c r="L37" s="5" t="s">
@@ -2403,9 +2390,9 @@
       <c r="C38" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="12" t="s">
-        <v>100</v>
+      <c r="D38" s="7"/>
+      <c r="E38" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>54</v>
@@ -2417,12 +2404,12 @@
         <v>95</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="J38" s="10">
+        <v>102</v>
+      </c>
+      <c r="J38" s="8">
         <v>1</v>
       </c>
-      <c r="K38" s="14">
+      <c r="K38" s="11">
         <v>539.75</v>
       </c>
       <c r="L38" s="5" t="s">
@@ -2445,9 +2432,9 @@
       <c r="C39" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="9"/>
-      <c r="E39" s="12" t="s">
-        <v>100</v>
+      <c r="D39" s="7"/>
+      <c r="E39" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>54</v>
@@ -2459,12 +2446,12 @@
         <v>97</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="J39" s="10">
+        <v>102</v>
+      </c>
+      <c r="J39" s="8">
         <v>1</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="11">
         <v>539.75</v>
       </c>
       <c r="L39" s="5" t="s">

--- a/data-vh/Неделя_20.07-26.07_2026_ВХ.xlsx
+++ b/data-vh/Неделя_20.07-26.07_2026_ВХ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F88A0A-1775-4D8E-8AC7-3B2C9AFF2F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFA252D-CC7D-442C-8717-565A93427310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="27870" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="106">
   <si>
     <t>№ п/п</t>
   </si>
@@ -338,9 +338,6 @@
   </si>
   <si>
     <t>МК, другое</t>
-  </si>
-  <si>
-    <t>2 221,5</t>
   </si>
   <si>
     <t>Поставщик/переработчик</t>
@@ -350,7 +347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <name val="Arial"/>
@@ -370,6 +367,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -445,7 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -485,6 +488,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -828,7 +834,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -2199,8 +2205,8 @@
       <c r="J33" s="8">
         <v>2</v>
       </c>
-      <c r="K33" s="12" t="s">
-        <v>105</v>
+      <c r="K33" s="14">
+        <v>2221.5</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>50</v>
